--- a/data/trans_dic/P16A_n_R3-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P16A_n_R3-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido cinco o más medicamentos en las dos últimas semanas</t>
+          <t>Población que ha consumido cinco o más medicamentos en las dos últimas semanas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,9</t>
+          <t>0,41; 2,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,56</t>
+          <t>0,6; 2,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,27; 3,59</t>
+          <t>1,29; 3,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,69; 7,98</t>
+          <t>4,59; 7,81</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,65</t>
+          <t>0,3; 1,75</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,25; 6,51</t>
+          <t>3,17; 6,42</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,57; 6,82</t>
+          <t>3,55; 6,85</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,64; 11,52</t>
+          <t>7,66; 11,37</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,49; 1,48</t>
+          <t>0,51; 1,53</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,1; 4,03</t>
+          <t>2,22; 4,08</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,63; 4,81</t>
+          <t>2,71; 4,72</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,79; 9,24</t>
+          <t>6,9; 9,26</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,89; 2,66</t>
+          <t>0,85; 2,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,15</t>
+          <t>0,65; 2,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,92; 2,62</t>
+          <t>0,93; 2,44</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,92; 4,94</t>
+          <t>1,64; 4,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,43; 3,39</t>
+          <t>1,4; 3,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,91; 6,69</t>
+          <t>3,83; 6,79</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,38; 4,81</t>
+          <t>2,31; 4,73</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,04; 10,79</t>
+          <t>8,03; 10,77</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,33; 2,58</t>
+          <t>1,31; 2,59</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,45; 4,05</t>
+          <t>2,49; 4,16</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,83; 3,28</t>
+          <t>1,88; 3,34</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,08; 7,3</t>
+          <t>3,98; 7,19</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,59</t>
+          <t>0,68; 2,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,34; 4,13</t>
+          <t>1,28; 4,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,07; 3,24</t>
+          <t>1,11; 3,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,63; 5,39</t>
+          <t>2,73; 5,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,72; 5,91</t>
+          <t>2,95; 5,85</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,53; 5,33</t>
+          <t>2,4; 5,21</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,61; 5,41</t>
+          <t>2,66; 5,55</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,85; 7,69</t>
+          <t>2,67; 7,61</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,02; 3,84</t>
+          <t>1,96; 3,74</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,19; 4,09</t>
+          <t>2,11; 4,13</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,19; 3,91</t>
+          <t>2,13; 3,94</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,1; 5,88</t>
+          <t>3,17; 5,87</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,24; 2,81</t>
+          <t>1,25; 2,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,5; 3,73</t>
+          <t>1,52; 3,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,05</t>
+          <t>0,63; 2,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,23; 6,76</t>
+          <t>4,19; 6,77</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,04; 4,21</t>
+          <t>2,04; 4,15</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,6; 7,73</t>
+          <t>4,62; 7,88</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,87; 6,72</t>
+          <t>3,86; 6,63</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,65; 12,8</t>
+          <t>8,57; 12,94</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,84; 3,25</t>
+          <t>1,86; 3,22</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,4; 5,19</t>
+          <t>3,37; 5,28</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,43; 4,14</t>
+          <t>2,46; 4,12</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7,21; 9,6</t>
+          <t>6,98; 9,55</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,12; 1,97</t>
+          <t>1,12; 1,92</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,34; 2,35</t>
+          <t>1,36; 2,37</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,27; 2,09</t>
+          <t>1,25; 2,1</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,57; 5,31</t>
+          <t>3,54; 5,25</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,05; 3,2</t>
+          <t>2,11; 3,18</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,33; 5,77</t>
+          <t>4,28; 5,73</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,6; 5,04</t>
+          <t>3,67; 5,17</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,12; 9,81</t>
+          <t>7,17; 9,86</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,71; 2,42</t>
+          <t>1,71; 2,4</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,95; 3,88</t>
+          <t>3,01; 3,9</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,58; 3,46</t>
+          <t>2,62; 3,49</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,88; 7,48</t>
+          <t>5,79; 7,44</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido cinco o más medicamentos en las dos últimas semanas</t>
+          <t>Población que ha consumido cinco o más medicamentos en las dos últimas semanas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2842; 13212</t>
+          <t>2856; 14136</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4432; 18004</t>
+          <t>4252; 16955</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8547; 24236</t>
+          <t>8714; 24682</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>29786; 50736</t>
+          <t>29196; 49632</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1958; 11354</t>
+          <t>2055; 12012</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22670; 45380</t>
+          <t>22075; 44780</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24035; 45862</t>
+          <t>23901; 46109</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>55387; 83533</t>
+          <t>55536; 82454</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6755; 20465</t>
+          <t>7092; 21089</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>29460; 56401</t>
+          <t>31064; 57100</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>35393; 64764</t>
+          <t>36476; 63652</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>92433; 125739</t>
+          <t>93851; 125991</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8583; 25537</t>
+          <t>8188; 25936</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6524; 21913</t>
+          <t>6620; 24310</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9378; 26776</t>
+          <t>9510; 24965</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22886; 58958</t>
+          <t>19600; 58047</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13849; 32855</t>
+          <t>13599; 33226</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>40319; 69061</t>
+          <t>39556; 70045</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>24779; 50127</t>
+          <t>24137; 49310</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>77070; 103402</t>
+          <t>76995; 103205</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>25701; 49736</t>
+          <t>25313; 50036</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>50313; 82938</t>
+          <t>50987; 85387</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>37701; 67796</t>
+          <t>38894; 68942</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>87857; 157142</t>
+          <t>85688; 154697</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4669; 17594</t>
+          <t>4642; 17802</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>10119; 31321</t>
+          <t>9702; 31265</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8158; 24603</t>
+          <t>8464; 23439</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18560; 37957</t>
+          <t>19252; 37794</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>18572; 40406</t>
+          <t>20160; 40032</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19629; 41391</t>
+          <t>18660; 40497</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20494; 42489</t>
+          <t>20850; 43556</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>26560; 71773</t>
+          <t>24888; 71006</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>27461; 52360</t>
+          <t>26642; 50922</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>33628; 62721</t>
+          <t>32406; 63323</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>33788; 60323</t>
+          <t>32887; 60845</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>50720; 96311</t>
+          <t>51878; 96184</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11723; 26444</t>
+          <t>11824; 27301</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14254; 35324</t>
+          <t>14412; 34741</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5982; 19217</t>
+          <t>5907; 19623</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>39213; 62618</t>
+          <t>38816; 62722</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>21182; 43773</t>
+          <t>21201; 43115</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>48382; 81267</t>
+          <t>48610; 82916</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>40399; 70183</t>
+          <t>40269; 69198</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>94759; 140146</t>
+          <t>93792; 141707</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>36394; 64416</t>
+          <t>36893; 63736</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>68067; 103760</t>
+          <t>67351; 105666</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>48246; 81980</t>
+          <t>48738; 81621</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>145669; 194190</t>
+          <t>141084; 193085</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>36592; 64528</t>
+          <t>36732; 62924</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>45861; 80691</t>
+          <t>46500; 81122</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>43049; 70937</t>
+          <t>42439; 71332</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>123430; 183887</t>
+          <t>122552; 181536</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>69379; 108246</t>
+          <t>71158; 107516</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>154178; 205263</t>
+          <t>152290; 203778</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>127474; 178651</t>
+          <t>130043; 183207</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>264499; 364092</t>
+          <t>266250; 365936</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>113981; 161115</t>
+          <t>113739; 160060</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>205742; 271287</t>
+          <t>210195; 272328</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>179161; 239935</t>
+          <t>181738; 242032</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>421523; 536767</t>
+          <t>415423; 533785</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A_n_R3-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P16A_n_R3-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,19%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,41; 2,04</t>
+          <t>0,41; 1,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,6; 2,41</t>
+          <t>0,61; 2,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,29; 3,66</t>
+          <t>1,37; 3,45</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,59; 7,81</t>
+          <t>4,57; 7,86</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,75</t>
+          <t>0,31; 1,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,17; 6,42</t>
+          <t>3,18; 6,47</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,55; 6,85</t>
+          <t>3,48; 6,95</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,66; 11,37</t>
+          <t>8,75; 12,02</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,51; 1,53</t>
+          <t>0,49; 1,54</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,22; 4,08</t>
+          <t>2,19; 3,97</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,71; 4,72</t>
+          <t>2,71; 4,7</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,9; 9,26</t>
+          <t>7,16; 9,47</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,7%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,85; 2,7</t>
+          <t>0,86; 2,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,39</t>
+          <t>0,56; 2,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,93; 2,44</t>
+          <t>0,9; 2,42</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,64; 4,87</t>
+          <t>3,26; 5,44</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,4; 3,43</t>
+          <t>1,42; 3,38</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,83; 6,79</t>
+          <t>3,87; 6,51</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,31; 4,73</t>
+          <t>2,27; 4,7</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,03; 10,77</t>
+          <t>7,97; 10,55</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,31; 2,59</t>
+          <t>1,33; 2,62</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,49; 4,16</t>
+          <t>2,47; 4,14</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,88; 3,34</t>
+          <t>1,79; 3,32</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,98; 7,19</t>
+          <t>5,85; 7,6</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>5,43%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,62</t>
+          <t>0,68; 2,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,28; 4,13</t>
+          <t>1,26; 4,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,11; 3,09</t>
+          <t>1,07; 3,11</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,73; 5,36</t>
+          <t>2,59; 5,25</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,95; 5,85</t>
+          <t>2,84; 5,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,4; 5,21</t>
+          <t>2,44; 5,18</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,66; 5,55</t>
+          <t>2,82; 5,8</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,67; 7,61</t>
+          <t>5,68; 8,61</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,96; 3,74</t>
+          <t>2,01; 3,74</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,11; 4,13</t>
+          <t>2,16; 4,12</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,13; 3,94</t>
+          <t>2,14; 3,99</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,17; 5,87</t>
+          <t>4,51; 6,53</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,42%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,25; 2,9</t>
+          <t>1,24; 2,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,52; 3,67</t>
+          <t>1,47; 3,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,09</t>
+          <t>0,64; 2,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,19; 6,77</t>
+          <t>4,12; 6,6</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,04; 4,15</t>
+          <t>2,04; 4,2</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,62; 7,88</t>
+          <t>4,61; 7,53</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,86; 6,63</t>
+          <t>3,76; 6,78</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,57; 12,94</t>
+          <t>9,85; 12,88</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,86; 3,22</t>
+          <t>1,88; 3,27</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,37; 5,28</t>
+          <t>3,39; 5,23</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,46; 4,12</t>
+          <t>2,48; 4,15</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,98; 9,55</t>
+          <t>7,47; 9,43</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>7,21%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,12; 1,92</t>
+          <t>1,12; 2,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,36; 2,37</t>
+          <t>1,36; 2,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,25; 2,1</t>
+          <t>1,23; 2,12</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,54; 5,25</t>
+          <t>4,15; 5,39</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,11; 3,18</t>
+          <t>2,1; 3,23</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,28; 5,73</t>
+          <t>4,26; 5,77</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,67; 5,17</t>
+          <t>3,66; 5,01</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,17; 9,86</t>
+          <t>8,86; 10,45</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,71; 2,4</t>
+          <t>1,72; 2,39</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,01; 3,9</t>
+          <t>3,0; 3,87</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,62; 3,49</t>
+          <t>2,63; 3,48</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,79; 7,44</t>
+          <t>6,72; 7,72</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>38620</t>
+          <t>41442</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>70552</t>
+          <t>75259</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>109172</t>
+          <t>116701</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2856; 14136</t>
+          <t>2832; 13273</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4252; 16955</t>
+          <t>4297; 17658</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8714; 24682</t>
+          <t>9259; 23288</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>29196; 49632</t>
+          <t>31570; 54324</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2055; 12012</t>
+          <t>2107; 12701</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22075; 44780</t>
+          <t>22152; 45096</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23901; 46109</t>
+          <t>23441; 46792</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>55536; 82454</t>
+          <t>64259; 88225</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>7092; 21089</t>
+          <t>6827; 21263</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>31064; 57100</t>
+          <t>30695; 55630</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>36476; 63652</t>
+          <t>36498; 63397</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>93851; 125991</t>
+          <t>101996; 134875</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>41727</t>
+          <t>44066</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>89673</t>
+          <t>97920</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>131400</t>
+          <t>141986</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8188; 25936</t>
+          <t>8317; 24066</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6620; 24310</t>
+          <t>5706; 21175</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9510; 24965</t>
+          <t>9170; 24756</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19600; 58047</t>
+          <t>34155; 57054</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13599; 33226</t>
+          <t>13732; 32700</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>39556; 70045</t>
+          <t>39905; 67180</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>24137; 49310</t>
+          <t>23662; 49021</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>76995; 103205</t>
+          <t>85389; 113036</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>25313; 50036</t>
+          <t>25605; 50505</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>50987; 85387</t>
+          <t>50571; 84855</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>38894; 68942</t>
+          <t>36875; 68574</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>85688; 154697</t>
+          <t>124120; 161198</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26716</t>
+          <t>29952</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>51157</t>
+          <t>57743</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>77873</t>
+          <t>87695</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4642; 17802</t>
+          <t>4635; 18046</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9702; 31265</t>
+          <t>9510; 31452</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8464; 23439</t>
+          <t>8124; 23595</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19252; 37794</t>
+          <t>20803; 42194</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>20160; 40032</t>
+          <t>19415; 39400</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18660; 40497</t>
+          <t>18943; 40252</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20850; 43556</t>
+          <t>22132; 45562</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>24888; 71006</t>
+          <t>46166; 69906</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>26642; 50922</t>
+          <t>27371; 51012</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>32406; 63323</t>
+          <t>33122; 63302</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>32887; 60845</t>
+          <t>33057; 61636</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>51878; 96184</t>
+          <t>72781; 105513</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>49474</t>
+          <t>51955</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>118423</t>
+          <t>125692</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>167897</t>
+          <t>177647</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11824; 27301</t>
+          <t>11728; 26604</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14412; 34741</t>
+          <t>13916; 36098</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5907; 19623</t>
+          <t>6010; 20282</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>38816; 62722</t>
+          <t>40784; 65387</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>21201; 43115</t>
+          <t>21141; 43654</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>48610; 82916</t>
+          <t>48503; 79177</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>40269; 69198</t>
+          <t>39237; 70744</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>93792; 141707</t>
+          <t>110179; 144143</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>36893; 63736</t>
+          <t>37329; 64782</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>67351; 105666</t>
+          <t>67820; 104571</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>48738; 81621</t>
+          <t>49080; 82301</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>141084; 193085</t>
+          <t>157499; 198936</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>156537</t>
+          <t>167415</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>329805</t>
+          <t>356614</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>486342</t>
+          <t>524028</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>36732; 62924</t>
+          <t>36699; 66042</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>46500; 81122</t>
+          <t>46738; 84898</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>42439; 71332</t>
+          <t>41897; 72025</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>122552; 181536</t>
+          <t>146648; 190405</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>71158; 107516</t>
+          <t>71073; 109134</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>152290; 203778</t>
+          <t>151751; 205189</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>130043; 183207</t>
+          <t>129772; 177696</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>266250; 365936</t>
+          <t>331277; 390470</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>113739; 160060</t>
+          <t>114323; 159065</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>210195; 272328</t>
+          <t>209642; 270618</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>181738; 242032</t>
+          <t>182546; 241787</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>415423; 533785</t>
+          <t>488369; 561122</t>
         </is>
       </c>
     </row>
